--- a/data/trans_orig/P25C_R_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dejó de fumar con o sin ayuda específica en 2023</t>
+          <t>Población según si dejó de fumar con o sin ayuda específica en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145368</t>
+          <t>145540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157471</t>
+          <t>157781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>39390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187476</t>
+          <t>186825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200934</t>
+          <t>200746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48350</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>25819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67278</t>
+          <t>67300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496057</t>
+          <t>495466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>538149</t>
+          <t>537336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>178286</t>
+          <t>177305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190430</t>
+          <t>190376</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680253</t>
+          <t>680231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730638</t>
+          <t>731577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125079</t>
+          <t>124075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134419</t>
+          <t>134098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73040</t>
+          <t>73438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82327</t>
+          <t>82303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201146</t>
+          <t>202077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214795</t>
+          <t>214917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67679</t>
+          <t>66632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21335</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37848</t>
+          <t>38005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>38285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96451</t>
+          <t>97193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>779802</t>
+          <t>780849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>830711</t>
+          <t>832050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296707</t>
+          <t>296550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>313220</t>
+          <t>313622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1085586</t>
+          <t>1084844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1144090</t>
+          <t>1143752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>24083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>152426</t>
+          <t>161989</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145540</t>
+          <t>153777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157781</t>
+          <t>167764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42542</t>
+          <t>45128</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39390</t>
+          <t>41740</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43774</t>
+          <t>46445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>194968</t>
+          <t>207117</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186825</t>
+          <t>199088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200746</t>
+          <t>213027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>176119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>176119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>176119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>210078</t>
+          <t>223171</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>210078</t>
+          <t>223171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>210078</t>
+          <t>223171</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41799</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15954</t>
+          <t>35811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67300</t>
+          <t>59938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>520698</t>
+          <t>305566</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495466</t>
+          <t>295329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>537336</t>
+          <t>314958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>185035</t>
+          <t>203052</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177305</t>
+          <t>195048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190376</t>
+          <t>209287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>705732</t>
+          <t>508618</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680231</t>
+          <t>494675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731577</t>
+          <t>518802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>544407</t>
+          <t>332490</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>544407</t>
+          <t>332490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>544407</t>
+          <t>332490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>203124</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203124</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203124</t>
+          <t>222123</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>747531</t>
+          <t>554613</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>747531</t>
+          <t>554613</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>747531</t>
+          <t>554613</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>17462</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>25628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>130672</t>
+          <t>140830</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124075</t>
+          <t>133834</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134098</t>
+          <t>144888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78442</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73438</t>
+          <t>79941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82303</t>
+          <t>90071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209114</t>
+          <t>226815</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202077</t>
+          <t>218649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214917</t>
+          <t>232749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>137335</t>
+          <t>148687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137335</t>
+          <t>148687</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137335</t>
+          <t>148687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>224427</t>
+          <t>244277</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>224427</t>
+          <t>244277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>224427</t>
+          <t>244277</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>37432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66632</t>
+          <t>62886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>40696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>72222</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38285</t>
+          <t>65136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97193</t>
+          <t>95866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>803796</t>
+          <t>608386</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>780849</t>
+          <t>594411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>832050</t>
+          <t>619865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>306019</t>
+          <t>334165</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296550</t>
+          <t>324068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>313622</t>
+          <t>341654</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1109815</t>
+          <t>942551</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1084844</t>
+          <t>926195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1143752</t>
+          <t>956925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>847481</t>
+          <t>657297</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>847481</t>
+          <t>657297</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>847481</t>
+          <t>657297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1182037</t>
+          <t>1022061</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1182037</t>
+          <t>1022061</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1182037</t>
+          <t>1022061</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
